--- a/data/trans_bre/IP08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 3,39</t>
+          <t>-11,64; 3,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 8,72</t>
+          <t>-8,84; 8,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 10,2</t>
+          <t>-2,23; 10,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 27,45</t>
+          <t>-14,69; 28,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,43; 49,96</t>
+          <t>-69,49; 49,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 104,79</t>
+          <t>-50,57; 95,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-54,32; 747,0</t>
+          <t>-50,88; 748,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 277,96</t>
+          <t>-72,45; 259,69</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -1,03</t>
+          <t>-6,98; -0,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,52</t>
+          <t>-5,48; 1,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,72</t>
+          <t>-3,96; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,83; -0,74</t>
+          <t>-12,0; -0,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,01; -9,03</t>
+          <t>-54,22; -6,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 12,8</t>
+          <t>-35,2; 11,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,64; 26,76</t>
+          <t>-42,63; 27,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,71; -5,52</t>
+          <t>-63,67; -7,94</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 3,66</t>
+          <t>-7,57; 3,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 2,67</t>
+          <t>-7,88; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 5,08</t>
+          <t>-2,76; 5,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 5,13</t>
+          <t>-7,36; 5,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,97; 40,22</t>
+          <t>-49,35; 38,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,93; 32,67</t>
+          <t>-55,13; 35,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 141,65</t>
+          <t>-40,07; 141,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,44; 56,64</t>
+          <t>-47,26; 63,17</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -0,74</t>
+          <t>-5,87; -0,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,82</t>
+          <t>-4,75; 0,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,95</t>
+          <t>-2,51; 1,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,05</t>
+          <t>-8,39; 0,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,54; -6,04</t>
+          <t>-45,52; -7,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 6,91</t>
+          <t>-31,49; 6,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 33,25</t>
+          <t>-31,72; 34,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,9; 2,9</t>
+          <t>-50,95; 1,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 3,88</t>
+          <t>-10,78; 4,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 8,6</t>
+          <t>-8,18; 9,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 10,19</t>
+          <t>-2,99; 10,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 28,85</t>
+          <t>-14,13; 26,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 49,59</t>
+          <t>-68,18; 61,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-50,57; 95,02</t>
+          <t>-46,86; 109,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,88; 748,22</t>
+          <t>-59,47; 718,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-72,45; 259,69</t>
+          <t>-74,86; 272,67</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,98; -0,77</t>
+          <t>-7,14; -0,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 1,5</t>
+          <t>-5,67; 1,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,72</t>
+          <t>-4,05; 1,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,0; -0,99</t>
+          <t>-11,0; -0,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,22; -6,01</t>
+          <t>-54,45; -9,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 11,66</t>
+          <t>-34,55; 10,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 27,83</t>
+          <t>-43,27; 20,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,67; -7,94</t>
+          <t>-61,38; -4,17</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 3,41</t>
+          <t>-7,97; 3,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 2,77</t>
+          <t>-8,42; 2,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 5,21</t>
+          <t>-2,78; 5,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 5,33</t>
+          <t>-7,33; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 38,12</t>
+          <t>-49,81; 36,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 35,22</t>
+          <t>-56,63; 23,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,07; 141,51</t>
+          <t>-37,25; 152,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 63,17</t>
+          <t>-46,91; 52,95</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -0,87</t>
+          <t>-5,86; -0,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,77</t>
+          <t>-4,82; 0,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,99</t>
+          <t>-2,53; 2,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 0,05</t>
+          <t>-7,89; 0,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,52; -7,13</t>
+          <t>-44,51; -7,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 6,6</t>
+          <t>-31,72; 7,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 34,75</t>
+          <t>-32,16; 34,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 1,17</t>
+          <t>-49,74; 3,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-7,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,46%</t>
+          <t>-44,97%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 4,33</t>
+          <t>-11,7; 3,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 9,51</t>
+          <t>-7,4; 8,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 10,5</t>
+          <t>-2,47; 10,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 26,66</t>
+          <t>-18,73; 3,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,18; 61,89</t>
+          <t>-70,43; 49,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 109,19</t>
+          <t>-43,54; 104,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,47; 718,66</t>
+          <t>-54,32; 747,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,86; 272,67</t>
+          <t>-80,57; 34,85</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,61</t>
+          <t>-3,86</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-36,03%</t>
+          <t>-30,74%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -0,97</t>
+          <t>-7,05; -1,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 1,23</t>
+          <t>-6,12; 1,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,39</t>
+          <t>-3,74; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -0,67</t>
+          <t>-9,77; 0,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,45; -9,86</t>
+          <t>-54,01; -9,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 10,16</t>
+          <t>-37,67; 12,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 20,91</t>
+          <t>-40,64; 26,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,38; -4,17</t>
+          <t>-55,78; 1,51</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-8,79%</t>
+          <t>-2,27%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 3,18</t>
+          <t>-8,33; 3,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 2,15</t>
+          <t>-8,09; 2,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 5,46</t>
+          <t>-2,94; 5,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 4,58</t>
+          <t>-6,25; 6,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 36,41</t>
+          <t>-51,97; 40,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,63; 23,89</t>
+          <t>-53,93; 32,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-37,25; 152,96</t>
+          <t>-41,24; 141,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 52,95</t>
+          <t>-43,55; 67,85</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-26,49%</t>
+          <t>-26,04%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,86</t>
+          <t>-5,92; -0,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,9</t>
+          <t>-4,87; 0,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,06</t>
+          <t>-2,54; 1,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 0,26</t>
+          <t>-7,46; -0,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,51; -7,33</t>
+          <t>-45,54; -6,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 7,49</t>
+          <t>-32,22; 6,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 34,95</t>
+          <t>-31,63; 33,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,74; 3,29</t>
+          <t>-46,63; -1,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,33</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,45</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-27,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>85,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-44,97%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-3.334078598071906</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.3976033978690841</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.452248214320619</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-7.660778473393962</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2792916649797067</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.02966873157428644</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.8543589801294007</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.4497039928470097</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-11,7; 3,39</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,4; 8,72</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,47; 10,2</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-18,73; 3,12</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-70,43; 49,96</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-43,54; 104,79</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-54,32; 747,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-80,57; 34,85</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-11.70218876719592</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.40316587178411</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.474597721286123</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-18.72810088808274</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7043090231022713</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4353698646386999</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.5431939541477545</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.8057167922513614</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.385227260273814</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.719912355172784</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.19715506948145</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.123390916240166</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.4996313790885669</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.047925174249714</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>7.470007846764095</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.3485413751557845</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-3,88</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,1</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,86</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-34,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-14,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-15,29%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-30,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,05; -1,03</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,12; 1,52</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,74; 1,72</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,77; 0,05</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-54,01; -9,03</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-37,67; 12,8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-40,64; 26,76</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-55,78; 1,51</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.875513332384124</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.100487617393057</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.210839555781098</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.858275175016437</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3454104633791182</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1475361408941126</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1528957839106321</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3074009215413525</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-17,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-22,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-2,27%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.054727647408201</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.115786323585972</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.744587309174613</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.772122456451331</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.540121051782901</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3766885782805612</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4063899633774111</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5577845373977466</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,33; 3,66</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,09; 2,67</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,94; 5,08</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,25; 6,13</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-51,97; 40,22</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-53,93; 32,67</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-41,24; 141,65</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-43,55; 67,85</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-1.026213525317726</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.52261816706385</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.717661314656918</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.05216547316747423</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.09026106358605968</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.127962298730535</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.2676243284551379</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.01511035133582643</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,31</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,31</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-28,64%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-14,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-26,04%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.174771627185228</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.710841697693019</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.312210417449662</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.2667424267898302</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1748411452846775</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2280411700244832</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.2413037321125182</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.0227127990635959</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,92; -0,74</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,87; 0,82</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 1,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,46; -0,28</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-45,54; -6,04</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-32,22; 6,91</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-31,63; 33,25</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-46,63; -1,78</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.334967375143561</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.088930288295197</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.938500233347587</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.250009071604993</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5197072343782061</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.539276207924377</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4123781990812117</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4355043178083285</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.656222796103623</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.666374906562209</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.078660419461001</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.130185866068608</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.4021588114487684</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3266668108266551</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.416468533620707</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.6784566833629221</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.31492896191465</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.942970424710465</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.1506005161089757</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.31206898604013</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2864219730139336</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1428241861220664</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.02171392135158616</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2603659962613969</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.915542948301836</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.871238074438885</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.540201451966159</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.461989381045759</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4554247931972775</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3222260271502837</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3163209210827836</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.466278626852805</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.7394006834270466</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8195769876306077</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.946767346675045</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-0.2807118796371463</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.06037359725312866</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.06908815335724827</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.3325198694159462</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-0.01784666300679893</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
